--- a/Backend/CenterBackend/Report/周报表/2026-03/周报表-2026年11周.xlsx
+++ b/Backend/CenterBackend/Report/周报表/2026-03/周报表-2026年11周.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="967" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" tabRatio="967" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="第一页" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="第十二页产品原料单耗" sheetId="12" r:id="rId12"/>
     <sheet name="第十三页周核心指标完成情况" sheetId="14" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
@@ -29,7 +29,10 @@
     <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2244,7 +2247,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+            <b/>
+          </rPr>
+          <t xml:space="preserve">熊茂盛:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+=当周检测数据取平均值，下同</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2581,7 +2610,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="300">
   <si>
     <t xml:space="preserve">设计参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3817,19 +3846,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">表3 二乙睛化分平均</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">表3 产量汇总最下角</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">水+二乙睛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">表5 新增列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">表4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4099,7 +4124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="83">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -4397,6 +4422,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="dotted">
         <color auto="1"/>
       </left>
@@ -4409,6 +4447,32 @@
     </border>
     <border>
       <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -4520,6 +4584,28 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5178,48 +5264,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5431,7 +5480,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5440,7 +5489,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5449,10 +5498,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5471,9 +5520,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5488,16 +5534,16 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5506,64 +5552,61 @@
     <xf numFmtId="176" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5572,28 +5615,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5605,7 +5636,7 @@
     <xf numFmtId="176" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5614,7 +5645,7 @@
     <xf numFmtId="176" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5629,7 +5660,7 @@
     <xf numFmtId="176" fontId="3" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5641,7 +5672,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5650,16 +5681,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="74" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="79" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5668,7 +5702,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5692,7 +5726,7 @@
     <xf numFmtId="176" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5713,25 +5747,25 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5749,426 +5783,429 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6611,9 +6648,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="1.84765625" customWidth="1"/>
+    <col min="1" max="1" width="1.86328125" customWidth="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6624,31 +6661,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <dimension ref="B2:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="2.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="5" width="19.59765625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.59765625" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1">
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-    </row>
-    <row r="4" spans="2:5" ht="25" customHeight="1">
-      <c r="B4" s="238" t="s">
+      <c r="B3" s="197"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+    </row>
+    <row r="4" spans="2:5" ht="25.05" customHeight="1">
+      <c r="B4" s="231" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="34" t="s">
@@ -6657,35 +6693,35 @@
       <c r="D4" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="239" t="s">
+      <c r="E4" s="232" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="25" customHeight="1">
-      <c r="B5" s="204"/>
+    <row r="5" spans="2:5" ht="25.05" customHeight="1">
+      <c r="B5" s="193"/>
       <c r="C5" s="53" t="s">
         <v>107</v>
       </c>
       <c r="D5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="240"/>
-    </row>
-    <row r="6" spans="2:5" ht="25" customHeight="1">
+      <c r="E5" s="233"/>
+    </row>
+    <row r="6" spans="2:5" ht="25.05" customHeight="1">
       <c r="B6" s="40" t="s">
         <v>105</v>
       </c>
       <c r="C6" s="53">
         <v>0</v>
       </c>
-      <c r="D6" s="119">
+      <c r="D6" s="53">
         <v>62</v>
       </c>
       <c r="E6" s="54">
         <v>301</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="25" customHeight="1">
+    <row r="7" spans="2:5" ht="25.05" customHeight="1">
       <c r="B7" s="55" t="s">
         <v>106</v>
       </c>
@@ -6700,13 +6736,13 @@
       </c>
     </row>
     <row r="8" spans="2:5" ht="15" customHeight="1">
-      <c r="B8" s="241"/>
-      <c r="C8" s="242"/>
-      <c r="D8" s="242"/>
-      <c r="E8" s="243"/>
-    </row>
-    <row r="9" spans="2:5" ht="25" customHeight="1">
-      <c r="B9" s="238" t="s">
+      <c r="B8" s="234"/>
+      <c r="C8" s="235"/>
+      <c r="D8" s="235"/>
+      <c r="E8" s="236"/>
+    </row>
+    <row r="9" spans="2:5" ht="25.05" customHeight="1">
+      <c r="B9" s="231" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="34" t="s">
@@ -6719,8 +6755,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="25" customHeight="1">
-      <c r="B10" s="204"/>
+    <row r="10" spans="2:5" ht="25.05" customHeight="1">
+      <c r="B10" s="193"/>
       <c r="C10" s="53" t="s">
         <v>56</v>
       </c>
@@ -6731,7 +6767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="25" customHeight="1">
+    <row r="11" spans="2:5" ht="25.05" customHeight="1">
       <c r="B11" s="40" t="s">
         <v>102</v>
       </c>
@@ -6745,21 +6781,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="25" customHeight="1">
+    <row r="12" spans="2:5" ht="25.05" customHeight="1">
       <c r="B12" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="119">
+      <c r="C12" s="53">
         <v>57</v>
       </c>
-      <c r="D12" s="119">
+      <c r="D12" s="53">
         <v>59</v>
       </c>
       <c r="E12" s="91">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="25" customHeight="1">
+    <row r="13" spans="2:5" ht="25.05" customHeight="1">
       <c r="B13" s="55" t="s">
         <v>104</v>
       </c>
@@ -6767,7 +6803,7 @@
         <f>C11-C12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D13" s="121" t="e">
+      <c r="D13" s="56" t="e">
         <f>D11-D12</f>
         <v>#VALUE!</v>
       </c>
@@ -6776,53 +6812,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="6:10">
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="6:10" ht="14.1" customHeight="1">
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="6:10">
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-    </row>
-    <row r="20" spans="6:10">
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-    </row>
-    <row r="21" spans="6:10">
-      <c r="F21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="120"/>
-    </row>
-    <row r="22" spans="6:10">
-      <c r="F22" s="120"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="120"/>
-      <c r="J22" s="120"/>
-    </row>
-    <row r="23" spans="6:10">
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-    </row>
+    <row r="18" ht="14.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B2:E2"/>
@@ -6845,134 +6835,134 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="2" max="2" width="20.265625" customWidth="1"/>
     <col min="3" max="5" width="15.59765625" customWidth="1"/>
-    <col min="6" max="6" width="12.94921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>167</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1">
-      <c r="B3" s="244"/>
-      <c r="C3" s="244"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
-    </row>
-    <row r="4" spans="2:6" s="1" customFormat="1" ht="25" customHeight="1">
+      <c r="B3" s="237"/>
+      <c r="C3" s="237"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+    </row>
+    <row r="4" spans="2:6" s="1" customFormat="1" ht="25.05" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="245"/>
-      <c r="D4" s="246"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="122" t="s">
+      <c r="C4" s="238"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="36" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:6" s="1" customFormat="1" ht="25" customHeight="1">
+    <row r="5" spans="2:6" s="1" customFormat="1" ht="25.05" customHeight="1">
       <c r="B5" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="248">
+      <c r="C5" s="241">
         <v>4340</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="250"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="243"/>
       <c r="F5" s="66" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:6" s="45" customFormat="1" ht="40.2" customHeight="1">
-      <c r="B6" s="165" t="s">
+    <row r="6" spans="2:6" s="45" customFormat="1" ht="40.25" customHeight="1">
+      <c r="B6" s="160" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="166" t="s">
+      <c r="D6" s="161" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="166" t="s">
+      <c r="E6" s="161" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="177" t="s">
+      <c r="F6" s="172" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="40.2" customHeight="1">
-      <c r="B7" s="93" t="s">
+    <row r="7" spans="2:6" ht="40.25" customHeight="1">
+      <c r="B7" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="167">
+      <c r="C7" s="162">
         <v>52</v>
       </c>
-      <c r="D7" s="167">
+      <c r="D7" s="162">
         <v>53</v>
       </c>
-      <c r="E7" s="167">
+      <c r="E7" s="162">
         <v>55</v>
       </c>
-      <c r="F7" s="178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="40.2" customHeight="1">
-      <c r="B8" s="168" t="s">
+      <c r="F7" s="173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="40.25" customHeight="1">
+      <c r="B8" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="167">
+      <c r="C8" s="162">
         <v>52</v>
       </c>
-      <c r="D8" s="167">
+      <c r="D8" s="162">
         <v>53</v>
       </c>
-      <c r="E8" s="167">
+      <c r="E8" s="162">
         <v>55</v>
       </c>
-      <c r="F8" s="178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="40.2" customHeight="1">
-      <c r="B9" s="168" t="s">
+      <c r="F8" s="173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="40.25" customHeight="1">
+      <c r="B9" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="167">
+      <c r="C9" s="162">
         <v>52</v>
       </c>
-      <c r="D9" s="167">
+      <c r="D9" s="162">
         <v>53</v>
       </c>
-      <c r="E9" s="167">
+      <c r="E9" s="162">
         <v>55</v>
       </c>
-      <c r="F9" s="178">
+      <c r="F9" s="173">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="169" t="s">
+      <c r="B10" s="164" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="251" t="s">
-        <v>286</v>
-      </c>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
+      <c r="C10" s="244" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="244"/>
+      <c r="E10" s="244"/>
+      <c r="F10" s="244"/>
     </row>
     <row r="11" spans="2:6">
       <c r="F11" s="0" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -6996,42 +6986,42 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:Y23"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="2.34765625" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.59765625" customWidth="1"/>
     <col min="3" max="10" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-    </row>
-    <row r="3" spans="2:24" ht="25" customHeight="1">
-      <c r="B3" s="275" t="s">
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+    </row>
+    <row r="3" spans="2:24" ht="25.05" customHeight="1">
+      <c r="B3" s="268" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="275"/>
-      <c r="D3" s="275"/>
-      <c r="E3" s="275"/>
-      <c r="F3" s="275"/>
-      <c r="G3" s="275"/>
-      <c r="H3" s="275"/>
-      <c r="I3" s="275"/>
-      <c r="J3" s="275"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="268"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
     </row>
     <row r="4" spans="2:24" ht="15" customHeight="1"/>
     <row r="5" spans="2:24" ht="30" customHeight="1">
-      <c r="B5" s="273" t="s">
+      <c r="B5" s="266" t="s">
         <v>112</v>
       </c>
       <c r="C5" s="75" t="s">
@@ -7059,8 +7049,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="25" customHeight="1">
-      <c r="B6" s="274"/>
+    <row r="6" spans="2:24" ht="25.05" customHeight="1">
+      <c r="B6" s="267"/>
       <c r="C6" s="5" t="s">
         <v>114</v>
       </c>
@@ -7086,7 +7076,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1">
+    <row r="7" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1">
       <c r="B7" s="16" t="s">
         <v>47</v>
       </c>
@@ -7115,7 +7105,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1">
+    <row r="8" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1">
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -7144,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1">
+    <row r="9" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>105</v>
       </c>
@@ -7173,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1">
+    <row r="10" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1" thickBot="1">
       <c r="B10" s="7" t="s">
         <v>106</v>
       </c>
@@ -7202,7 +7192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1">
+    <row r="11" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1" thickBot="1">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7211,262 +7201,262 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1">
-      <c r="B12" s="276">
+    <row r="12" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1">
+      <c r="B12" s="269">
         <v>2025</v>
       </c>
-      <c r="C12" s="277"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="278" t="s">
+      <c r="C12" s="270"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="271" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="278"/>
-      <c r="G12" s="277"/>
-      <c r="H12" s="277"/>
-      <c r="I12" s="277"/>
-      <c r="J12" s="277"/>
-      <c r="K12" s="277"/>
-      <c r="L12" s="277"/>
-      <c r="M12" s="277"/>
-      <c r="N12" s="277"/>
-      <c r="O12" s="277"/>
-      <c r="P12" s="277"/>
-      <c r="Q12" s="277"/>
-      <c r="R12" s="277"/>
-      <c r="S12" s="277"/>
-      <c r="T12" s="277"/>
-      <c r="U12" s="277"/>
-      <c r="V12" s="277"/>
-      <c r="W12" s="277"/>
-      <c r="X12" s="279"/>
-    </row>
-    <row r="13" spans="2:24" s="1" customFormat="1" ht="25" customHeight="1">
-      <c r="B13" s="269" t="s">
+      <c r="F12" s="271"/>
+      <c r="G12" s="270"/>
+      <c r="H12" s="270"/>
+      <c r="I12" s="270"/>
+      <c r="J12" s="270"/>
+      <c r="K12" s="270"/>
+      <c r="L12" s="270"/>
+      <c r="M12" s="270"/>
+      <c r="N12" s="270"/>
+      <c r="O12" s="270"/>
+      <c r="P12" s="270"/>
+      <c r="Q12" s="270"/>
+      <c r="R12" s="270"/>
+      <c r="S12" s="270"/>
+      <c r="T12" s="270"/>
+      <c r="U12" s="270"/>
+      <c r="V12" s="270"/>
+      <c r="W12" s="270"/>
+      <c r="X12" s="272"/>
+    </row>
+    <row r="13" spans="2:24" s="1" customFormat="1" ht="25.05" customHeight="1">
+      <c r="B13" s="262" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="264" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="271" t="s">
+      <c r="D13" s="264" t="s">
         <v>211</v>
       </c>
-      <c r="E13" s="259" t="s">
+      <c r="E13" s="252" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="260"/>
-      <c r="G13" s="257" t="s">
+      <c r="F13" s="253"/>
+      <c r="G13" s="250" t="s">
         <v>212</v>
       </c>
-      <c r="H13" s="258"/>
-      <c r="I13" s="267" t="s">
+      <c r="H13" s="251"/>
+      <c r="I13" s="260" t="s">
         <v>213</v>
       </c>
-      <c r="J13" s="268"/>
-      <c r="K13" s="257" t="s">
+      <c r="J13" s="261"/>
+      <c r="K13" s="250" t="s">
         <v>214</v>
       </c>
-      <c r="L13" s="258"/>
-      <c r="M13" s="259" t="s">
+      <c r="L13" s="251"/>
+      <c r="M13" s="252" t="s">
         <v>215</v>
       </c>
-      <c r="N13" s="260"/>
-      <c r="O13" s="257" t="s">
+      <c r="N13" s="253"/>
+      <c r="O13" s="250" t="s">
         <v>216</v>
       </c>
-      <c r="P13" s="258"/>
-      <c r="Q13" s="259" t="s">
+      <c r="P13" s="251"/>
+      <c r="Q13" s="252" t="s">
         <v>217</v>
       </c>
-      <c r="R13" s="260"/>
-      <c r="S13" s="257" t="s">
+      <c r="R13" s="253"/>
+      <c r="S13" s="250" t="s">
         <v>218</v>
       </c>
-      <c r="T13" s="258"/>
-      <c r="U13" s="259" t="s">
+      <c r="T13" s="251"/>
+      <c r="U13" s="252" t="s">
         <v>219</v>
       </c>
-      <c r="V13" s="260"/>
-      <c r="W13" s="258" t="s">
+      <c r="V13" s="253"/>
+      <c r="W13" s="251" t="s">
         <v>220</v>
       </c>
-      <c r="X13" s="261"/>
-    </row>
-    <row r="14" spans="2:24" ht="25" customHeight="1">
-      <c r="B14" s="270"/>
-      <c r="C14" s="272"/>
-      <c r="D14" s="272"/>
-      <c r="E14" s="124" t="s">
+      <c r="X13" s="254"/>
+    </row>
+    <row r="14" spans="2:24" ht="25.05" customHeight="1">
+      <c r="B14" s="263"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="265"/>
+      <c r="E14" s="118" t="s">
         <v>221</v>
       </c>
-      <c r="F14" s="124" t="s">
+      <c r="F14" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="112" t="s">
+      <c r="G14" s="111" t="s">
         <v>221</v>
       </c>
-      <c r="H14" s="112" t="s">
+      <c r="H14" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="124" t="s">
+      <c r="I14" s="118" t="s">
         <v>221</v>
       </c>
-      <c r="J14" s="124" t="s">
+      <c r="J14" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="K14" s="112" t="s">
+      <c r="K14" s="111" t="s">
         <v>222</v>
       </c>
-      <c r="L14" s="112" t="s">
+      <c r="L14" s="111" t="s">
         <v>223</v>
       </c>
-      <c r="M14" s="124" t="s">
+      <c r="M14" s="118" t="s">
         <v>222</v>
       </c>
-      <c r="N14" s="124" t="s">
+      <c r="N14" s="118" t="s">
         <v>223</v>
       </c>
-      <c r="O14" s="112" t="s">
+      <c r="O14" s="111" t="s">
         <v>222</v>
       </c>
-      <c r="P14" s="112" t="s">
+      <c r="P14" s="111" t="s">
         <v>223</v>
       </c>
-      <c r="Q14" s="124" t="s">
+      <c r="Q14" s="118" t="s">
         <v>222</v>
       </c>
-      <c r="R14" s="124" t="s">
+      <c r="R14" s="118" t="s">
         <v>223</v>
       </c>
-      <c r="S14" s="112" t="s">
+      <c r="S14" s="111" t="s">
         <v>222</v>
       </c>
-      <c r="T14" s="112" t="s">
+      <c r="T14" s="111" t="s">
         <v>223</v>
       </c>
-      <c r="U14" s="124" t="s">
+      <c r="U14" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="V14" s="124" t="s">
+      <c r="V14" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="W14" s="112" t="s">
+      <c r="W14" s="111" t="s">
         <v>225</v>
       </c>
-      <c r="X14" s="125" t="s">
+      <c r="X14" s="119" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:24">
-      <c r="B15" s="262">
+      <c r="B15" s="255">
         <v>1201</v>
       </c>
-      <c r="C15" s="217" t="s">
+      <c r="C15" s="206" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="115" t="s">
+      <c r="D15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126" t="s">
+      <c r="E15" s="120"/>
+      <c r="F15" s="120" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127" t="s">
+      <c r="G15" s="121"/>
+      <c r="H15" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126" t="s">
+      <c r="I15" s="120"/>
+      <c r="J15" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="128"/>
-      <c r="L15" s="127" t="s">
+      <c r="K15" s="122"/>
+      <c r="L15" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="M15" s="126"/>
-      <c r="N15" s="126" t="s">
+      <c r="M15" s="120"/>
+      <c r="N15" s="120" t="s">
         <v>113</v>
       </c>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127" t="s">
+      <c r="O15" s="121"/>
+      <c r="P15" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="Q15" s="128"/>
-      <c r="R15" s="126" t="s">
+      <c r="Q15" s="122"/>
+      <c r="R15" s="120" t="s">
         <v>113</v>
       </c>
-      <c r="S15" s="128"/>
-      <c r="T15" s="127" t="s">
+      <c r="S15" s="122"/>
+      <c r="T15" s="121" t="s">
         <v>227</v>
       </c>
-      <c r="U15" s="126"/>
-      <c r="V15" s="126" t="s">
+      <c r="U15" s="120"/>
+      <c r="V15" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="W15" s="127">
+      <c r="W15" s="121">
         <v>1</v>
       </c>
-      <c r="X15" s="129" t="s">
+      <c r="X15" s="123" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:24">
-      <c r="B16" s="263"/>
-      <c r="C16" s="265"/>
-      <c r="D16" s="130" t="s">
+      <c r="B16" s="256"/>
+      <c r="C16" s="258"/>
+      <c r="D16" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131" t="s">
+      <c r="E16" s="125"/>
+      <c r="F16" s="125" t="s">
         <v>113</v>
       </c>
       <c r="G16" s="64"/>
       <c r="H16" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131" t="s">
+      <c r="I16" s="125"/>
+      <c r="J16" s="125" t="s">
         <v>113</v>
       </c>
       <c r="K16" s="64"/>
       <c r="L16" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131" t="s">
+      <c r="M16" s="125"/>
+      <c r="N16" s="125" t="s">
         <v>113</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="131" t="s">
+      <c r="Q16" s="125"/>
+      <c r="R16" s="125" t="s">
         <v>113</v>
       </c>
       <c r="S16" s="64"/>
       <c r="T16" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="U16" s="131"/>
-      <c r="V16" s="131" t="s">
+      <c r="U16" s="125"/>
+      <c r="V16" s="125" t="s">
         <v>113</v>
       </c>
       <c r="W16" s="64"/>
-      <c r="X16" s="132" t="s">
+      <c r="X16" s="126" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="17" spans="2:24">
-      <c r="B17" s="263"/>
-      <c r="C17" s="265"/>
-      <c r="D17" s="133" t="s">
+      <c r="B17" s="256"/>
+      <c r="C17" s="258"/>
+      <c r="D17" s="127" t="s">
         <v>230</v>
       </c>
-      <c r="E17" s="131" t="e">
+      <c r="E17" s="125" t="e">
         <f>E15/E16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F17" s="131" t="s">
+      <c r="F17" s="125" t="s">
         <v>114</v>
       </c>
       <c r="G17" s="64" t="e">
@@ -7476,11 +7466,11 @@
       <c r="H17" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="131" t="e">
+      <c r="I17" s="125" t="e">
         <f>I15/I16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J17" s="131" t="s">
+      <c r="J17" s="125" t="s">
         <v>115</v>
       </c>
       <c r="K17" s="64" t="e">
@@ -7490,11 +7480,11 @@
       <c r="L17" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="131" t="e">
+      <c r="M17" s="125" t="e">
         <f>M15/M16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N17" s="131" t="s">
+      <c r="N17" s="125" t="s">
         <v>114</v>
       </c>
       <c r="O17" s="64" t="e">
@@ -7504,11 +7494,11 @@
       <c r="P17" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="Q17" s="131" t="e">
+      <c r="Q17" s="125" t="e">
         <f>Q15/Q16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R17" s="131" t="s">
+      <c r="R17" s="125" t="s">
         <v>114</v>
       </c>
       <c r="S17" s="64" t="e">
@@ -7518,128 +7508,128 @@
       <c r="T17" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="U17" s="131" t="e">
+      <c r="U17" s="125" t="e">
         <f>U15/U16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V17" s="131" t="s">
+      <c r="V17" s="125" t="s">
         <v>232</v>
       </c>
       <c r="W17" s="64" t="e">
         <f>W15/W16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X17" s="132" t="s">
+      <c r="X17" s="126" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="18" spans="2:24">
-      <c r="B18" s="263"/>
-      <c r="C18" s="265" t="s">
+      <c r="B18" s="256"/>
+      <c r="C18" s="258" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131" t="s">
+      <c r="E18" s="125"/>
+      <c r="F18" s="125" t="s">
         <v>113</v>
       </c>
       <c r="G18" s="64"/>
       <c r="H18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="131"/>
-      <c r="J18" s="131" t="s">
+      <c r="I18" s="125"/>
+      <c r="J18" s="125" t="s">
         <v>100</v>
       </c>
-      <c r="K18" s="134"/>
+      <c r="K18" s="128"/>
       <c r="L18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="M18" s="131"/>
-      <c r="N18" s="131" t="s">
+      <c r="M18" s="125"/>
+      <c r="N18" s="125" t="s">
         <v>113</v>
       </c>
       <c r="O18" s="64"/>
       <c r="P18" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="Q18" s="134"/>
-      <c r="R18" s="131" t="s">
+      <c r="Q18" s="128"/>
+      <c r="R18" s="125" t="s">
         <v>113</v>
       </c>
-      <c r="S18" s="134"/>
+      <c r="S18" s="128"/>
       <c r="T18" s="64" t="s">
         <v>227</v>
       </c>
-      <c r="U18" s="131"/>
-      <c r="V18" s="131" t="s">
+      <c r="U18" s="125"/>
+      <c r="V18" s="125" t="s">
         <v>100</v>
       </c>
       <c r="W18" s="64"/>
-      <c r="X18" s="132" t="s">
+      <c r="X18" s="126" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="2:24">
-      <c r="B19" s="263"/>
-      <c r="C19" s="265"/>
-      <c r="D19" s="130" t="s">
+      <c r="B19" s="256"/>
+      <c r="C19" s="258"/>
+      <c r="D19" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131" t="s">
+      <c r="E19" s="125"/>
+      <c r="F19" s="125" t="s">
         <v>113</v>
       </c>
       <c r="G19" s="64"/>
       <c r="H19" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="131"/>
-      <c r="J19" s="131" t="s">
+      <c r="I19" s="125"/>
+      <c r="J19" s="125" t="s">
         <v>113</v>
       </c>
       <c r="K19" s="64"/>
       <c r="L19" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="M19" s="131"/>
-      <c r="N19" s="131" t="s">
+      <c r="M19" s="125"/>
+      <c r="N19" s="125" t="s">
         <v>113</v>
       </c>
       <c r="O19" s="64"/>
       <c r="P19" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="Q19" s="131"/>
-      <c r="R19" s="131" t="s">
+      <c r="Q19" s="125"/>
+      <c r="R19" s="125" t="s">
         <v>113</v>
       </c>
       <c r="S19" s="64"/>
       <c r="T19" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="U19" s="131"/>
-      <c r="V19" s="131" t="s">
+      <c r="U19" s="125"/>
+      <c r="V19" s="125" t="s">
         <v>113</v>
       </c>
       <c r="W19" s="64"/>
-      <c r="X19" s="132" t="s">
+      <c r="X19" s="126" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="20" spans="2:24">
-      <c r="B20" s="264"/>
-      <c r="C20" s="266"/>
-      <c r="D20" s="135" t="s">
+      <c r="B20" s="257"/>
+      <c r="C20" s="259"/>
+      <c r="D20" s="129" t="s">
         <v>230</v>
       </c>
-      <c r="E20" s="136" t="e">
+      <c r="E20" s="130" t="e">
         <f>E18/E19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F20" s="136" t="s">
+      <c r="F20" s="130" t="s">
         <v>114</v>
       </c>
       <c r="G20" s="65" t="e">
@@ -7649,11 +7639,11 @@
       <c r="H20" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="I20" s="136" t="e">
+      <c r="I20" s="130" t="e">
         <f>I18/I19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J20" s="136" t="s">
+      <c r="J20" s="130" t="s">
         <v>115</v>
       </c>
       <c r="K20" s="65" t="e">
@@ -7663,11 +7653,11 @@
       <c r="L20" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="M20" s="136" t="e">
+      <c r="M20" s="130" t="e">
         <f>M18/M19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="136" t="s">
+      <c r="N20" s="130" t="s">
         <v>114</v>
       </c>
       <c r="O20" s="65" t="e">
@@ -7677,11 +7667,11 @@
       <c r="P20" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="Q20" s="136" t="e">
+      <c r="Q20" s="130" t="e">
         <f>Q18/Q19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R20" s="136" t="s">
+      <c r="R20" s="130" t="s">
         <v>114</v>
       </c>
       <c r="S20" s="65" t="e">
@@ -7691,243 +7681,243 @@
       <c r="T20" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="U20" s="136" t="e">
+      <c r="U20" s="130" t="e">
         <f>U18/U19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V20" s="136" t="s">
+      <c r="V20" s="130" t="s">
         <v>115</v>
       </c>
       <c r="W20" s="65" t="e">
         <f>W18/W19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X20" s="137" t="s">
+      <c r="X20" s="131" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="21" spans="2:24">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="245" t="s">
         <v>234</v>
       </c>
-      <c r="C21" s="253"/>
-      <c r="D21" s="253"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="139" t="s">
+      <c r="C21" s="246"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="133" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="140">
+      <c r="G21" s="134">
         <f>G15+G18</f>
         <v>0</v>
       </c>
       <c r="H21" s="99" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="138">
+      <c r="I21" s="132">
         <f>I15+I18</f>
         <v>0</v>
       </c>
-      <c r="J21" s="139" t="s">
+      <c r="J21" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="140">
+      <c r="K21" s="134">
         <f>K15+K18</f>
         <v>0</v>
       </c>
       <c r="L21" s="99" t="s">
         <v>229</v>
       </c>
-      <c r="M21" s="138">
+      <c r="M21" s="132">
         <f>M15+M18</f>
         <v>0</v>
       </c>
-      <c r="N21" s="139" t="s">
+      <c r="N21" s="133" t="s">
         <v>229</v>
       </c>
-      <c r="O21" s="140">
+      <c r="O21" s="134">
         <f>O15+O18</f>
         <v>0</v>
       </c>
       <c r="P21" s="99" t="s">
         <v>229</v>
       </c>
-      <c r="Q21" s="138">
+      <c r="Q21" s="132">
         <f>Q15+Q18</f>
         <v>0</v>
       </c>
-      <c r="R21" s="139" t="s">
+      <c r="R21" s="133" t="s">
         <v>229</v>
       </c>
-      <c r="S21" s="140">
+      <c r="S21" s="134">
         <f>S15+S18</f>
         <v>0</v>
       </c>
       <c r="T21" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="U21" s="138">
+      <c r="U21" s="132">
         <f>U15+U18</f>
         <v>0</v>
       </c>
-      <c r="V21" s="139" t="s">
+      <c r="V21" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="W21" s="140">
+      <c r="W21" s="134">
         <f>W15+W18</f>
         <v>1</v>
       </c>
-      <c r="X21" s="141" t="s">
+      <c r="X21" s="135" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="B22" s="254" t="s">
+      <c r="B22" s="247" t="s">
         <v>237</v>
       </c>
-      <c r="C22" s="227"/>
-      <c r="D22" s="227"/>
-      <c r="E22" s="142"/>
+      <c r="C22" s="216"/>
+      <c r="D22" s="216"/>
+      <c r="E22" s="136"/>
       <c r="F22" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="G22" s="143">
+      <c r="G22" s="137">
         <f>G16+G19</f>
         <v>0</v>
       </c>
-      <c r="H22" s="97" t="s">
+      <c r="H22" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="I22" s="142">
+      <c r="I22" s="136">
         <f>I16+I19</f>
         <v>0</v>
       </c>
       <c r="J22" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="K22" s="143">
+      <c r="K22" s="137">
         <f>K16+K19</f>
         <v>0</v>
       </c>
-      <c r="L22" s="97" t="s">
+      <c r="L22" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="M22" s="142">
+      <c r="M22" s="136">
         <f>M16+M19</f>
         <v>0</v>
       </c>
       <c r="N22" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="O22" s="143">
+      <c r="O22" s="137">
         <f>O16+O19</f>
         <v>0</v>
       </c>
-      <c r="P22" s="97" t="s">
+      <c r="P22" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="Q22" s="142">
+      <c r="Q22" s="136">
         <f>Q16+Q19</f>
         <v>0</v>
       </c>
       <c r="R22" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="S22" s="143">
+      <c r="S22" s="137">
         <f>S16+S19</f>
         <v>0</v>
       </c>
-      <c r="T22" s="97" t="s">
+      <c r="T22" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="U22" s="142">
+      <c r="U22" s="136">
         <f>U16+U19</f>
         <v>0</v>
       </c>
       <c r="V22" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="W22" s="143">
+      <c r="W22" s="137">
         <f>W16+W19</f>
         <v>0</v>
       </c>
-      <c r="X22" s="144" t="s">
+      <c r="X22" s="138" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="2:24" ht="14.4" thickBot="1">
-      <c r="B23" s="255" t="s">
+    <row r="23" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B23" s="248" t="s">
         <v>238</v>
       </c>
-      <c r="C23" s="256"/>
-      <c r="D23" s="256"/>
-      <c r="E23" s="145" t="e">
+      <c r="C23" s="249"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="139" t="e">
         <f>E21/E22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F23" s="145" t="s">
+      <c r="F23" s="139" t="s">
         <v>239</v>
       </c>
-      <c r="G23" s="146" t="e">
+      <c r="G23" s="140" t="e">
         <f>G21/G22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="146" t="s">
+      <c r="H23" s="140" t="s">
         <v>239</v>
       </c>
-      <c r="I23" s="145" t="e">
+      <c r="I23" s="139" t="e">
         <f>I21/I22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J23" s="145" t="s">
+      <c r="J23" s="139" t="s">
         <v>232</v>
       </c>
-      <c r="K23" s="146" t="e">
+      <c r="K23" s="140" t="e">
         <f>K21/K22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="146" t="s">
+      <c r="L23" s="140" t="s">
         <v>239</v>
       </c>
-      <c r="M23" s="145" t="e">
+      <c r="M23" s="139" t="e">
         <f>M21/M22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N23" s="145" t="s">
+      <c r="N23" s="139" t="s">
         <v>239</v>
       </c>
-      <c r="O23" s="146" t="e">
+      <c r="O23" s="140" t="e">
         <f>O21/O22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P23" s="146" t="s">
+      <c r="P23" s="140" t="s">
         <v>239</v>
       </c>
-      <c r="Q23" s="145" t="e">
+      <c r="Q23" s="139" t="e">
         <f>Q21/Q22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R23" s="145" t="s">
+      <c r="R23" s="139" t="s">
         <v>239</v>
       </c>
-      <c r="S23" s="146" t="e">
+      <c r="S23" s="140" t="e">
         <f>S21/S22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T23" s="146" t="s">
+      <c r="T23" s="140" t="s">
         <v>240</v>
       </c>
-      <c r="U23" s="145" t="e">
+      <c r="U23" s="139" t="e">
         <f>U21/U22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V23" s="145" t="s">
+      <c r="V23" s="139" t="s">
         <v>232</v>
       </c>
-      <c r="W23" s="146" t="e">
+      <c r="W23" s="140" t="e">
         <f>W21/W22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X23" s="147" t="s">
+      <c r="X23" s="141" t="s">
         <v>232</v>
       </c>
     </row>
@@ -7970,30 +7960,42 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B2:M30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="B2:S30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.94921875" style="2" customWidth="1"/>
-    <col min="3" max="12" width="13.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="5.59765625" style="2" customWidth="1"/>
+    <col min="10" max="11" width="8.59765625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" style="2" customWidth="1"/>
+    <col min="14" max="15" width="6.59765625" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.59765625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="21.73046875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+    <row r="2" spans="2:18" ht="30" customHeight="1">
+      <c r="B2" s="176" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-    </row>
-    <row r="3" spans="2:12" ht="30" customHeight="1">
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
+      <c r="N2" s="176"/>
+      <c r="O2" s="176"/>
+      <c r="P2" s="176"/>
+      <c r="Q2" s="176"/>
+      <c r="R2" s="176"/>
+    </row>
+    <row r="3" spans="2:18" ht="30" customHeight="1">
       <c r="B3" s="291" t="s">
         <v>145</v>
       </c>
@@ -8007,8 +8009,14 @@
       <c r="J3" s="291"/>
       <c r="K3" s="291"/>
       <c r="L3" s="291"/>
-    </row>
-    <row r="4" spans="2:12" ht="10" customHeight="1">
+      <c r="M3" s="291"/>
+      <c r="N3" s="291"/>
+      <c r="O3" s="291"/>
+      <c r="P3" s="291"/>
+      <c r="Q3" s="291"/>
+      <c r="R3" s="291"/>
+    </row>
+    <row r="4" spans="2:18" ht="10.05" customHeight="1">
       <c r="B4" s="289"/>
       <c r="C4" s="290"/>
       <c r="D4" s="290"/>
@@ -8020,567 +8028,730 @@
       <c r="J4" s="290"/>
       <c r="K4" s="290"/>
       <c r="L4" s="290"/>
-    </row>
-    <row r="5" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B5" s="308" t="s">
+      <c r="M4" s="290"/>
+      <c r="N4" s="290"/>
+      <c r="O4" s="290"/>
+      <c r="P4" s="290"/>
+      <c r="Q4" s="290"/>
+      <c r="R4" s="290"/>
+    </row>
+    <row r="5" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="288" t="s">
+      <c r="C5" s="287" t="s">
         <v>135</v>
       </c>
       <c r="D5" s="294" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="294" t="s">
+      <c r="E5" s="295"/>
+      <c r="F5" s="294" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="294" t="s">
+      <c r="G5" s="295"/>
+      <c r="H5" s="294" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="294" t="s">
+      <c r="I5" s="295"/>
+      <c r="J5" s="294" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="296" t="s">
+      <c r="K5" s="295"/>
+      <c r="L5" s="298" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="284" t="s">
+      <c r="M5" s="279" t="s">
         <v>163</v>
       </c>
-      <c r="J5" s="301" t="s">
+      <c r="N5" s="303" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="301" t="s">
+      <c r="O5" s="295"/>
+      <c r="P5" s="303" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="302" t="s">
+      <c r="Q5" s="295"/>
+      <c r="R5" s="308" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B6" s="309"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="295"/>
-      <c r="E6" s="295"/>
-      <c r="F6" s="295"/>
-      <c r="G6" s="295"/>
-      <c r="H6" s="297"/>
-      <c r="I6" s="253"/>
-      <c r="J6" s="295"/>
-      <c r="K6" s="295"/>
-      <c r="L6" s="206"/>
-    </row>
-    <row r="7" spans="2:12" ht="12.6" customHeight="1">
-      <c r="B7" s="310"/>
-      <c r="C7" s="272"/>
-      <c r="D7" s="182" t="s">
+    <row r="6" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B6" s="283">
+        <v>45992</v>
+      </c>
+      <c r="C6" s="226"/>
+      <c r="D6" s="296"/>
+      <c r="E6" s="297"/>
+      <c r="F6" s="296"/>
+      <c r="G6" s="297"/>
+      <c r="H6" s="296"/>
+      <c r="I6" s="297"/>
+      <c r="J6" s="296"/>
+      <c r="K6" s="297"/>
+      <c r="L6" s="299"/>
+      <c r="M6" s="246"/>
+      <c r="N6" s="296"/>
+      <c r="O6" s="297"/>
+      <c r="P6" s="296"/>
+      <c r="Q6" s="297"/>
+      <c r="R6" s="195"/>
+    </row>
+    <row r="7" spans="2:18" ht="13.9">
+      <c r="B7" s="276"/>
+      <c r="C7" s="265"/>
+      <c r="D7" s="273" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="182" t="s">
+      <c r="E7" s="274"/>
+      <c r="F7" s="273" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="182" t="s">
+      <c r="G7" s="274"/>
+      <c r="H7" s="273" t="s">
         <v>156</v>
       </c>
-      <c r="G7" s="182" t="s">
+      <c r="I7" s="274"/>
+      <c r="J7" s="273" t="s">
         <v>157</v>
       </c>
-      <c r="H7" s="285"/>
-      <c r="I7" s="71" t="s">
+      <c r="K7" s="274"/>
+      <c r="L7" s="280"/>
+      <c r="M7" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="182" t="s">
+      <c r="N7" s="273" t="s">
         <v>164</v>
       </c>
-      <c r="K7" s="182" t="s">
+      <c r="O7" s="274"/>
+      <c r="P7" s="273" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="303"/>
-    </row>
-    <row r="8" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B8" s="282" t="s">
-        <v>293</v>
+      <c r="Q7" s="274"/>
+      <c r="R7" s="309"/>
+    </row>
+    <row r="8" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B8" s="277" t="s">
+        <v>292</v>
       </c>
       <c r="C8" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D8" s="180">
-        <v>0</v>
-      </c>
-      <c r="E8" s="180">
-        <v>0</v>
-      </c>
-      <c r="F8" s="180">
-        <v>0</v>
-      </c>
-      <c r="G8" s="180">
-        <v>0</v>
-      </c>
-      <c r="H8" s="286" t="s">
-        <v>284</v>
-      </c>
-      <c r="I8" s="181">
+      <c r="D8" s="72">
+        <v>0</v>
+      </c>
+      <c r="E8" s="285">
+        <v>0</v>
+      </c>
+      <c r="F8" s="72">
+        <v>0</v>
+      </c>
+      <c r="G8" s="285">
+        <v>0</v>
+      </c>
+      <c r="H8" s="72"/>
+      <c r="I8" s="285">
         <v>310</v>
       </c>
-      <c r="J8" s="181">
+      <c r="J8" s="72">
         <v>83.09999084472656</v>
       </c>
-      <c r="K8" s="181">
+      <c r="K8" s="285">
         <v>26.80645179748535</v>
       </c>
-      <c r="L8" s="292"/>
-    </row>
-    <row r="9" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B9" s="283"/>
+      <c r="L8" s="285" t="s">
+        <v>283</v>
+      </c>
+      <c r="M8" s="142"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="304"/>
+      <c r="P8" s="142"/>
+      <c r="Q8" s="304"/>
+      <c r="R8" s="292"/>
+    </row>
+    <row r="9" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B9" s="278"/>
       <c r="C9" s="73" t="s">
         <v>144</v>
       </c>
       <c r="D9" s="73">
         <v>0</v>
       </c>
-      <c r="E9" s="73">
+      <c r="E9" s="286">
         <v>0</v>
       </c>
       <c r="F9" s="73">
         <v>0</v>
       </c>
-      <c r="G9" s="73">
-        <v>0</v>
-      </c>
-      <c r="H9" s="306"/>
-      <c r="I9" s="148">
+      <c r="G9" s="286">
+        <v>0</v>
+      </c>
+      <c r="H9" s="73"/>
+      <c r="I9" s="288">
         <v>310</v>
       </c>
-      <c r="J9" s="148">
+      <c r="J9" s="73">
         <v>83.09999084472656</v>
       </c>
-      <c r="K9" s="148">
+      <c r="K9" s="288">
         <v>26.80645179748535</v>
       </c>
-      <c r="L9" s="293"/>
-    </row>
-    <row r="10" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B10" s="222" t="s">
-        <v>294</v>
+      <c r="L9" s="288"/>
+      <c r="M9" s="143"/>
+      <c r="N9" s="143"/>
+      <c r="O9" s="305"/>
+      <c r="P9" s="143"/>
+      <c r="Q9" s="305"/>
+      <c r="R9" s="293"/>
+    </row>
+    <row r="10" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B10" s="211" t="s">
+        <v>293</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="183">
-        <v>0</v>
-      </c>
-      <c r="E10" s="183">
-        <v>0</v>
-      </c>
-      <c r="F10" s="183">
-        <v>0</v>
-      </c>
-      <c r="G10" s="183">
-        <v>0</v>
-      </c>
-      <c r="H10" s="284"/>
-      <c r="I10" s="181">
+      <c r="D10" s="35">
+        <v>0</v>
+      </c>
+      <c r="E10" s="287">
+        <v>0</v>
+      </c>
+      <c r="F10" s="35">
+        <v>0</v>
+      </c>
+      <c r="G10" s="287">
+        <v>0</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="279">
         <v>310</v>
       </c>
-      <c r="J10" s="181">
+      <c r="J10" s="35">
         <v>83.09999084472656</v>
       </c>
-      <c r="K10" s="181">
+      <c r="K10" s="279">
         <v>26.80645179748535</v>
       </c>
-      <c r="L10" s="298"/>
-    </row>
-    <row r="11" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B11" s="287"/>
+      <c r="L10" s="279"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="306"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="306"/>
+      <c r="R10" s="300"/>
+    </row>
+    <row r="11" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B11" s="284"/>
       <c r="C11" s="8" t="s">
         <v>144</v>
       </c>
       <c r="D11" s="8">
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="288">
         <v>0</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
       </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="307"/>
-      <c r="I11" s="148">
+      <c r="G11" s="288">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="280">
         <v>310</v>
       </c>
-      <c r="J11" s="148">
+      <c r="J11" s="8">
         <v>83.09999084472656</v>
       </c>
-      <c r="K11" s="148">
+      <c r="K11" s="280">
         <v>26.80645179748535</v>
       </c>
-      <c r="L11" s="304"/>
-    </row>
-    <row r="12" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B12" s="282" t="s">
-        <v>295</v>
+      <c r="L11" s="280"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="307"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="307"/>
+      <c r="R11" s="310"/>
+    </row>
+    <row r="12" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B12" s="277" t="s">
+        <v>294</v>
       </c>
       <c r="C12" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="180">
-        <v>0</v>
-      </c>
-      <c r="E12" s="180">
-        <v>0</v>
-      </c>
-      <c r="F12" s="180">
-        <v>0</v>
-      </c>
-      <c r="G12" s="180">
-        <v>0</v>
-      </c>
-      <c r="H12" s="286"/>
-      <c r="I12" s="181">
+      <c r="D12" s="72">
+        <v>0</v>
+      </c>
+      <c r="E12" s="285">
+        <v>0</v>
+      </c>
+      <c r="F12" s="72">
+        <v>0</v>
+      </c>
+      <c r="G12" s="285">
+        <v>0</v>
+      </c>
+      <c r="H12" s="72"/>
+      <c r="I12" s="281">
         <v>310</v>
       </c>
-      <c r="J12" s="181">
+      <c r="J12" s="72">
         <v>83.09999084472656</v>
       </c>
-      <c r="K12" s="181">
+      <c r="K12" s="281">
         <v>26.80645179748535</v>
       </c>
-      <c r="L12" s="298"/>
-    </row>
-    <row r="13" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B13" s="283"/>
+      <c r="L12" s="281"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="306"/>
+      <c r="P12" s="142"/>
+      <c r="Q12" s="306"/>
+      <c r="R12" s="300"/>
+    </row>
+    <row r="13" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B13" s="278"/>
       <c r="C13" s="73" t="s">
         <v>144</v>
       </c>
       <c r="D13" s="73">
         <v>0</v>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="286">
         <v>0</v>
       </c>
       <c r="F13" s="73">
         <v>0</v>
       </c>
-      <c r="G13" s="73">
-        <v>0</v>
-      </c>
-      <c r="H13" s="306"/>
-      <c r="I13" s="148">
+      <c r="G13" s="286">
+        <v>0</v>
+      </c>
+      <c r="H13" s="73"/>
+      <c r="I13" s="280">
         <v>310</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="73">
         <v>83.09999084472656</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="280">
         <v>26.80645179748535</v>
       </c>
-      <c r="L13" s="304"/>
-    </row>
-    <row r="14" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B14" s="280" t="s">
-        <v>296</v>
+      <c r="L13" s="280"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
+      <c r="O13" s="307"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="307"/>
+      <c r="R13" s="310"/>
+    </row>
+    <row r="14" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B14" s="275" t="s">
+        <v>295</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="184">
-        <v>0</v>
-      </c>
-      <c r="E14" s="184">
-        <v>0</v>
-      </c>
-      <c r="F14" s="184">
-        <v>0</v>
-      </c>
-      <c r="G14" s="184">
-        <v>0</v>
-      </c>
-      <c r="H14" s="284"/>
-      <c r="I14" s="149">
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="282">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="282">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="279">
         <v>310</v>
       </c>
-      <c r="J14" s="149">
+      <c r="J14" s="11">
         <v>83.09999084472656</v>
       </c>
-      <c r="K14" s="149">
+      <c r="K14" s="279">
         <v>26.80645179748535</v>
       </c>
-      <c r="L14" s="298"/>
-    </row>
-    <row r="15" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B15" s="281"/>
+      <c r="L14" s="279"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="306"/>
+      <c r="P14" s="144"/>
+      <c r="Q14" s="306"/>
+      <c r="R14" s="300"/>
+    </row>
+    <row r="15" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B15" s="276"/>
       <c r="C15" s="71" t="s">
         <v>144</v>
       </c>
       <c r="D15" s="71">
         <v>0</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="265">
         <v>0</v>
       </c>
       <c r="F15" s="71">
         <v>0</v>
       </c>
-      <c r="G15" s="71">
-        <v>0</v>
-      </c>
-      <c r="H15" s="307"/>
-      <c r="I15" s="150">
+      <c r="G15" s="265">
+        <v>0</v>
+      </c>
+      <c r="H15" s="71"/>
+      <c r="I15" s="299">
         <v>310</v>
       </c>
-      <c r="J15" s="150">
+      <c r="J15" s="71">
         <v>83.09999084472656</v>
       </c>
-      <c r="K15" s="150">
+      <c r="K15" s="299">
         <v>26.80645179748535</v>
       </c>
       <c r="L15" s="299"/>
-    </row>
-    <row r="16" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B16" s="282" t="s">
-        <v>297</v>
+      <c r="M15" s="145"/>
+      <c r="N15" s="145"/>
+      <c r="O15" s="312"/>
+      <c r="P15" s="145"/>
+      <c r="Q15" s="312"/>
+      <c r="R15" s="301"/>
+    </row>
+    <row r="16" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B16" s="277" t="s">
+        <v>296</v>
       </c>
       <c r="C16" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="180">
-        <v>0</v>
-      </c>
-      <c r="E16" s="180">
-        <v>0</v>
-      </c>
-      <c r="F16" s="180">
-        <v>0</v>
-      </c>
-      <c r="G16" s="180">
-        <v>0</v>
-      </c>
-      <c r="H16" s="286"/>
-      <c r="I16" s="181">
+      <c r="D16" s="72">
+        <v>0</v>
+      </c>
+      <c r="E16" s="285">
+        <v>0</v>
+      </c>
+      <c r="F16" s="72">
+        <v>0</v>
+      </c>
+      <c r="G16" s="285">
+        <v>0</v>
+      </c>
+      <c r="H16" s="72"/>
+      <c r="I16" s="285">
         <v>310</v>
       </c>
-      <c r="J16" s="181">
+      <c r="J16" s="72">
         <v>83.09999084472656</v>
       </c>
-      <c r="K16" s="181">
+      <c r="K16" s="285">
         <v>26.80645179748535</v>
       </c>
-      <c r="L16" s="292"/>
-    </row>
-    <row r="17" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B17" s="283"/>
+      <c r="L16" s="285"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="304"/>
+      <c r="P16" s="142"/>
+      <c r="Q16" s="142"/>
+      <c r="R16" s="292"/>
+    </row>
+    <row r="17" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B17" s="278"/>
       <c r="C17" s="73" t="s">
         <v>144</v>
       </c>
       <c r="D17" s="73">
         <v>0</v>
       </c>
-      <c r="E17" s="73">
+      <c r="E17" s="286">
         <v>0</v>
       </c>
       <c r="F17" s="73">
         <v>0</v>
       </c>
-      <c r="G17" s="73">
-        <v>0</v>
-      </c>
-      <c r="H17" s="306"/>
-      <c r="I17" s="148">
+      <c r="G17" s="286">
+        <v>0</v>
+      </c>
+      <c r="H17" s="73"/>
+      <c r="I17" s="288">
         <v>310</v>
       </c>
-      <c r="J17" s="148">
+      <c r="J17" s="73">
         <v>83.09999084472656</v>
       </c>
-      <c r="K17" s="148">
+      <c r="K17" s="288">
         <v>26.80645179748535</v>
       </c>
-      <c r="L17" s="293"/>
-    </row>
-    <row r="18" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B18" s="280" t="s">
-        <v>298</v>
+      <c r="L17" s="288"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="143"/>
+      <c r="O17" s="305"/>
+      <c r="P17" s="143"/>
+      <c r="Q17" s="143"/>
+      <c r="R17" s="293"/>
+    </row>
+    <row r="18" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B18" s="275" t="s">
+        <v>297</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="184">
-        <v>0</v>
-      </c>
-      <c r="E18" s="184">
-        <v>0</v>
-      </c>
-      <c r="F18" s="184">
-        <v>0</v>
-      </c>
-      <c r="G18" s="184">
-        <v>0</v>
-      </c>
-      <c r="H18" s="284"/>
-      <c r="I18" s="149">
+      <c r="D18" s="11">
+        <v>0</v>
+      </c>
+      <c r="E18" s="282">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="282">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="314">
         <v>310</v>
       </c>
-      <c r="J18" s="149">
+      <c r="J18" s="11">
         <v>83.09999084472656</v>
       </c>
-      <c r="K18" s="149">
+      <c r="K18" s="314">
         <v>26.80645179748535</v>
       </c>
-      <c r="L18" s="300"/>
-    </row>
-    <row r="19" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B19" s="281"/>
+      <c r="L18" s="314"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="311"/>
+      <c r="P18" s="144"/>
+      <c r="Q18" s="311"/>
+      <c r="R18" s="302"/>
+    </row>
+    <row r="19" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B19" s="276"/>
       <c r="C19" s="71" t="s">
         <v>144</v>
       </c>
       <c r="D19" s="71">
         <v>0</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="265">
         <v>0</v>
       </c>
       <c r="F19" s="71">
         <v>0</v>
       </c>
-      <c r="G19" s="71">
-        <v>0</v>
-      </c>
-      <c r="H19" s="307"/>
-      <c r="I19" s="150">
+      <c r="G19" s="265">
+        <v>0</v>
+      </c>
+      <c r="H19" s="71"/>
+      <c r="I19" s="299">
         <v>310</v>
       </c>
-      <c r="J19" s="150">
+      <c r="J19" s="71">
         <v>83.09999084472656</v>
       </c>
-      <c r="K19" s="150">
+      <c r="K19" s="299">
         <v>26.80645179748535</v>
       </c>
       <c r="L19" s="299"/>
-    </row>
-    <row r="20" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B20" s="282" t="s">
-        <v>299</v>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="312"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="312"/>
+      <c r="R19" s="301"/>
+    </row>
+    <row r="20" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B20" s="277" t="s">
+        <v>298</v>
       </c>
       <c r="C20" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="180">
-        <v>0</v>
-      </c>
-      <c r="E20" s="180">
-        <v>0</v>
-      </c>
-      <c r="F20" s="180">
-        <v>0</v>
-      </c>
-      <c r="G20" s="180">
-        <v>0</v>
-      </c>
-      <c r="H20" s="286"/>
-      <c r="I20" s="181">
+      <c r="D20" s="72">
+        <v>0</v>
+      </c>
+      <c r="E20" s="285">
+        <v>0</v>
+      </c>
+      <c r="F20" s="72">
+        <v>0</v>
+      </c>
+      <c r="G20" s="285">
+        <v>0</v>
+      </c>
+      <c r="H20" s="72"/>
+      <c r="I20" s="285">
         <v>310</v>
       </c>
-      <c r="J20" s="181">
+      <c r="J20" s="72">
         <v>83.09999084472656</v>
       </c>
-      <c r="K20" s="181">
+      <c r="K20" s="285">
         <v>26.80645179748535</v>
       </c>
-      <c r="L20" s="292"/>
-    </row>
-    <row r="21" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B21" s="283"/>
+      <c r="L20" s="285"/>
+      <c r="M20" s="142"/>
+      <c r="N20" s="142"/>
+      <c r="O20" s="304"/>
+      <c r="P20" s="142"/>
+      <c r="Q20" s="304"/>
+      <c r="R20" s="292"/>
+    </row>
+    <row r="21" spans="2:18" ht="15.6" customHeight="1">
+      <c r="B21" s="278"/>
       <c r="C21" s="73" t="s">
         <v>144</v>
       </c>
       <c r="D21" s="73">
         <v>0</v>
       </c>
-      <c r="E21" s="73">
+      <c r="E21" s="286">
         <v>0</v>
       </c>
       <c r="F21" s="73">
         <v>0</v>
       </c>
-      <c r="G21" s="73">
-        <v>0</v>
-      </c>
-      <c r="H21" s="306"/>
-      <c r="I21" s="148">
+      <c r="G21" s="286">
+        <v>0</v>
+      </c>
+      <c r="H21" s="73"/>
+      <c r="I21" s="288">
         <v>310</v>
       </c>
-      <c r="J21" s="148">
+      <c r="J21" s="73">
         <v>83.09999084472656</v>
       </c>
-      <c r="K21" s="148">
+      <c r="K21" s="288">
         <v>26.80645179748535</v>
       </c>
-      <c r="L21" s="293"/>
-    </row>
-    <row r="22" spans="2:12" ht="15.6" customHeight="1">
-      <c r="I22" s="151"/>
-      <c r="J22" s="151"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="151"/>
-    </row>
-    <row r="23" spans="2:12" ht="15.6" customHeight="1">
-      <c r="I23" s="305" t="s">
-        <v>285</v>
-      </c>
-      <c r="J23" s="305"/>
-      <c r="K23" s="305"/>
-    </row>
-    <row r="24" spans="2:12" ht="15.6" customHeight="1">
-      <c r="H24" s="151"/>
-      <c r="I24" s="151"/>
-      <c r="J24" s="151"/>
-      <c r="K24" s="151"/>
-    </row>
-    <row r="25" spans="2:12" ht="15.6" customHeight="1"/>
-    <row r="26" spans="2:12" ht="15.6" customHeight="1"/>
-    <row r="27" spans="2:12" ht="15.6" customHeight="1"/>
-    <row r="28" spans="2:12" ht="15.6" customHeight="1"/>
-    <row r="29" spans="2:12" ht="15.6" customHeight="1"/>
-    <row r="30" spans="2:12" ht="15.6" customHeight="1"/>
+      <c r="L21" s="288"/>
+      <c r="M21" s="143"/>
+      <c r="N21" s="143"/>
+      <c r="O21" s="305"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="305"/>
+      <c r="R21" s="293"/>
+    </row>
+    <row r="22" spans="2:18" ht="15.6" customHeight="1">
+      <c r="M22" s="146"/>
+      <c r="N22" s="146"/>
+      <c r="O22" s="146"/>
+      <c r="P22" s="146"/>
+      <c r="Q22" s="146"/>
+      <c r="R22" s="146"/>
+    </row>
+    <row r="23" spans="2:18" ht="15.6" customHeight="1">
+      <c r="M23" s="313" t="s">
+        <v>284</v>
+      </c>
+      <c r="N23" s="313"/>
+      <c r="O23" s="313"/>
+      <c r="P23" s="313"/>
+      <c r="Q23" s="313"/>
+    </row>
+    <row r="24" spans="2:18" ht="15.6" customHeight="1">
+      <c r="L24" s="146"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="146"/>
+      <c r="O24" s="146"/>
+      <c r="P24" s="146"/>
+      <c r="Q24" s="146"/>
+    </row>
+    <row r="25" spans="2:18" ht="15.6" customHeight="1"/>
+    <row r="26" spans="2:18" ht="15.6" customHeight="1"/>
+    <row r="27" spans="2:18" ht="15.6" customHeight="1"/>
+    <row r="28" spans="2:18" ht="15.6" customHeight="1"/>
+    <row r="29" spans="2:18" ht="15.6" customHeight="1"/>
+    <row r="30" spans="2:18" ht="15.6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
+  <mergeCells count="83">
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="Q20:Q21"/>
     <mergeCell ref="L14:L15"/>
     <mergeCell ref="L16:L17"/>
     <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="O20:O21"/>
     <mergeCell ref="L20:L21"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="R12:R13"/>
+    <mergeCell ref="B4:R4"/>
+    <mergeCell ref="B3:R3"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="J5:K6"/>
+    <mergeCell ref="J7:K7"/>
     <mergeCell ref="L5:L7"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H5:I6"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="H7:I7"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8590,37 +8761,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="B2:L18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="1.59765625" style="2" customWidth="1"/>
     <col min="2" max="10" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="27.75" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
     </row>
     <row r="3" spans="2:11" ht="15" customHeight="1">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
     </row>
     <row r="4" spans="2:11" ht="30" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -8654,7 +8825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="25" customHeight="1">
+    <row r="5" spans="2:11" ht="25.05" customHeight="1">
       <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
@@ -8686,7 +8857,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="25" customHeight="1">
+    <row r="6" spans="2:11" ht="25.05" customHeight="1">
       <c r="B6" s="16" t="s">
         <v>0</v>
       </c>
@@ -8718,7 +8889,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="25" customHeight="1">
+    <row r="7" spans="2:11" ht="25.05" customHeight="1">
       <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
@@ -8746,7 +8917,7 @@
       <c r="J7" s="27"/>
       <c r="K7" s="29"/>
     </row>
-    <row r="8" spans="2:11" ht="25" customHeight="1">
+    <row r="8" spans="2:11" ht="25.05" customHeight="1">
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
@@ -8774,7 +8945,7 @@
       <c r="J8" s="27"/>
       <c r="K8" s="29"/>
     </row>
-    <row r="9" spans="2:11" ht="25" customHeight="1">
+    <row r="9" spans="2:11" ht="25.05" customHeight="1">
       <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
@@ -8883,60 +9054,60 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="B2:I12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="7" width="11.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="2" customWidth="1"/>
+    <col min="2" max="7" width="11.265625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.46484375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="17.7">
-      <c r="B2" s="187" t="s">
+    <row r="2" spans="2:8" ht="17.65">
+      <c r="B2" s="176" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-    </row>
-    <row r="4" spans="2:8" ht="25.2" customHeight="1">
-      <c r="B4" s="85" t="s">
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+    </row>
+    <row r="4" spans="2:8" ht="25.25" customHeight="1">
+      <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="190" t="s">
+      <c r="D4" s="178"/>
+      <c r="E4" s="179" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="191"/>
-      <c r="G4" s="93" t="s">
+      <c r="F4" s="180"/>
+      <c r="G4" s="92" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="25.2">
-      <c r="B5" s="86"/>
-      <c r="C5" s="87" t="s">
+    <row r="5" spans="2:8" ht="25.5">
+      <c r="B5" s="85"/>
+      <c r="C5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="93" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="87" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="51">
@@ -8951,12 +9122,12 @@
       <c r="F6" s="51">
         <v>14</v>
       </c>
-      <c r="G6" s="95">
+      <c r="G6" s="94">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="38">
@@ -8976,7 +9147,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="38">
@@ -8996,7 +9167,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C9" s="38"/>
@@ -9006,7 +9177,7 @@
       <c r="G9" s="41"/>
     </row>
     <row r="10" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B10" s="93" t="s">
+      <c r="B10" s="92" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="41">
@@ -9030,23 +9201,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14.1">
-      <c r="B11" s="120" t="s">
+    <row r="11" spans="2:8" ht="13.9">
+      <c r="B11" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="120" t="s">
+      <c r="C11" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D11" s="120" t="s">
+      <c r="D11" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E11" s="120" t="s">
+      <c r="E11" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="120" t="s">
+      <c r="F11" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G11" s="152" t="s">
+      <c r="G11" s="147" t="s">
         <v>251</v>
       </c>
     </row>
@@ -9085,32 +9256,32 @@
   <dimension ref="B2:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.1" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.34765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="10.75" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="10.73046875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="17.1" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
     </row>
     <row r="3" spans="2:10" ht="17.1" customHeight="1">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
     </row>
     <row r="4" spans="2:10" ht="17.1" customHeight="1">
       <c r="B4" s="42" t="s">
@@ -9295,34 +9466,34 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="17.1" customHeight="1">
-      <c r="B11" s="192" t="s">
+      <c r="B11" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="193"/>
-      <c r="D11" s="193"/>
-      <c r="E11" s="193"/>
-      <c r="F11" s="193"/>
-      <c r="G11" s="193"/>
-      <c r="H11" s="193"/>
-      <c r="I11" s="194"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="183"/>
     </row>
     <row r="12" spans="2:10" ht="17.1" customHeight="1">
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="120" t="s">
+      <c r="C12" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D12" s="120" t="s">
+      <c r="D12" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="120" t="s">
+      <c r="E12" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G12" s="120" t="s">
+      <c r="G12" s="1" t="s">
         <v>256</v>
       </c>
     </row>
@@ -9351,53 +9522,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:R18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="B2:K18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.75" style="2" customWidth="1"/>
-    <col min="2" max="3" width="9.44921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.73046875" style="2" customWidth="1"/>
+    <col min="2" max="3" width="9.46484375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="7.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.44921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.46484375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="7.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.44921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="9" style="2"/>
+    <col min="10" max="10" width="9.46484375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+    <row r="2" spans="2:10" ht="30" customHeight="1">
+      <c r="B2" s="176" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-    </row>
-    <row r="3" spans="2:17" ht="15" customHeight="1">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-    </row>
-    <row r="4" spans="2:17" ht="25" customHeight="1">
-      <c r="B4" s="200" t="s">
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+    </row>
+    <row r="3" spans="2:10" ht="15" customHeight="1">
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+    </row>
+    <row r="4" spans="2:10" ht="25.05" customHeight="1">
+      <c r="B4" s="189" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="184" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="198" t="s">
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="187" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="198"/>
-      <c r="I4" s="198"/>
-      <c r="J4" s="199"/>
-    </row>
-    <row r="5" spans="2:17" ht="25" customHeight="1">
-      <c r="B5" s="201"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="188"/>
+    </row>
+    <row r="5" spans="2:10" ht="25.05" customHeight="1">
+      <c r="B5" s="190"/>
       <c r="C5" s="100" t="s">
         <v>21</v>
       </c>
@@ -9423,8 +9593,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="25" customHeight="1">
-      <c r="B6" s="202"/>
+    <row r="6" spans="2:10" ht="25.05" customHeight="1">
+      <c r="B6" s="191"/>
       <c r="C6" s="100">
         <v>21</v>
       </c>
@@ -9450,7 +9620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="25" customHeight="1">
+    <row r="7" spans="2:10" ht="25.05" customHeight="1">
       <c r="B7" s="102" t="s">
         <v>60</v>
       </c>
@@ -9460,11 +9630,11 @@
       <c r="D7" s="103">
         <v>23</v>
       </c>
-      <c r="E7" s="170">
+      <c r="E7" s="165">
         <f>C7+D7</f>
         <v>2</v>
       </c>
-      <c r="F7" s="170">
+      <c r="F7" s="165">
         <f>100-E7</f>
         <v>98</v>
       </c>
@@ -9474,16 +9644,16 @@
       <c r="H7" s="103">
         <v>33</v>
       </c>
-      <c r="I7" s="170">
+      <c r="I7" s="165">
         <f>G7+H7</f>
         <v>3</v>
       </c>
-      <c r="J7" s="171">
+      <c r="J7" s="166">
         <f>100-I7</f>
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="25" customHeight="1">
+    <row r="8" spans="2:10" ht="25.05" customHeight="1">
       <c r="B8" s="104" t="s">
         <v>64</v>
       </c>
@@ -9516,7 +9686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="25" customHeight="1">
+    <row r="9" spans="2:10" ht="25.05" customHeight="1">
       <c r="B9" s="107" t="s">
         <v>190</v>
       </c>
@@ -9549,42 +9719,39 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="25" customHeight="1">
-      <c r="B10" s="120" t="s">
+    <row r="10" spans="2:10" ht="25.05" customHeight="1">
+      <c r="B10" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="120">
+      <c r="C10" s="1">
         <v>21</v>
       </c>
-      <c r="D10" s="152">
+      <c r="D10" s="147">
         <v>23</v>
       </c>
-      <c r="E10" s="172">
+      <c r="E10" s="167">
         <v>24</v>
       </c>
-      <c r="F10" s="172">
+      <c r="F10" s="167">
         <v>25</v>
       </c>
-      <c r="G10" s="120">
+      <c r="G10" s="1">
         <v>31</v>
       </c>
-      <c r="H10" s="152">
+      <c r="H10" s="147">
         <v>33</v>
       </c>
-      <c r="I10" s="173">
+      <c r="I10" s="168">
         <v>34</v>
       </c>
-      <c r="J10" s="173">
+      <c r="J10" s="168">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="25" customHeight="1">
+    <row r="11" spans="2:10" ht="25.05" customHeight="1">
       <c r="E11" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="16" spans="2:17">
-      <c r="Q16" s="110"/>
     </row>
     <row r="17" ht="14.1" customHeight="1"/>
     <row r="18" ht="14.1" customHeight="1"/>
@@ -9605,38 +9772,37 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:Z26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <dimension ref="B2:X26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="40.046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="40.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.59765625" style="1" customWidth="1"/>
     <col min="8" max="22" width="9" style="1"/>
-    <col min="23" max="23" width="8.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9" style="1"/>
+    <col min="23" max="23" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+    <row r="2" spans="2:23" ht="30" customHeight="1">
+      <c r="B2" s="176" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-    </row>
-    <row r="3" spans="2:25" ht="15" customHeight="1">
-      <c r="B3" s="186"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-    </row>
-    <row r="4" spans="2:25" ht="25" customHeight="1">
-      <c r="B4" s="203" t="s">
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+    </row>
+    <row r="3" spans="2:23" ht="15" customHeight="1">
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+    </row>
+    <row r="4" spans="2:23" ht="25.05" customHeight="1">
+      <c r="B4" s="192" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="34" t="s">
@@ -9648,12 +9814,12 @@
       <c r="E4" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="205" t="s">
+      <c r="F4" s="194" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="2:25" ht="25" customHeight="1">
-      <c r="B5" s="204"/>
+    <row r="5" spans="2:23" ht="25.05" customHeight="1">
+      <c r="B5" s="193"/>
       <c r="C5" s="53" t="s">
         <v>56</v>
       </c>
@@ -9663,9 +9829,9 @@
       <c r="E5" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="206"/>
-    </row>
-    <row r="6" spans="2:25" ht="25" customHeight="1">
+      <c r="F5" s="195"/>
+    </row>
+    <row r="6" spans="2:23" ht="25.05" customHeight="1">
       <c r="B6" s="40" t="s">
         <v>63</v>
       </c>
@@ -9673,7 +9839,7 @@
         <v>26.806453704833984</v>
       </c>
       <c r="D6" s="53">
-        <v>0</v>
+        <v>27.806453704833984</v>
       </c>
       <c r="E6" s="53">
         <f>C6-D6</f>
@@ -9681,7 +9847,7 @@
       </c>
       <c r="F6" s="54"/>
     </row>
-    <row r="7" spans="2:25" ht="25" customHeight="1">
+    <row r="7" spans="2:23" ht="25.05" customHeight="1">
       <c r="B7" s="40" t="s">
         <v>64</v>
       </c>
@@ -9689,7 +9855,7 @@
         <v>26.806453704833984</v>
       </c>
       <c r="D7" s="53">
-        <v>0</v>
+        <v>27.806453704833984</v>
       </c>
       <c r="E7" s="53">
         <f>C7-D7</f>
@@ -9697,7 +9863,7 @@
       </c>
       <c r="F7" s="54"/>
     </row>
-    <row r="8" spans="2:25" ht="25" customHeight="1">
+    <row r="8" spans="2:23" ht="25.05" customHeight="1">
       <c r="B8" s="58" t="s">
         <v>65</v>
       </c>
@@ -9705,7 +9871,7 @@
         <v>26.806453704833984</v>
       </c>
       <c r="D8" s="59">
-        <v>0</v>
+        <v>27.806453704833984</v>
       </c>
       <c r="E8" s="59">
         <f>C8-D8</f>
@@ -9713,337 +9879,329 @@
       </c>
       <c r="F8" s="60"/>
     </row>
-    <row r="9" spans="2:25" ht="25" customHeight="1">
+    <row r="9" spans="2:23" ht="25.05" customHeight="1">
       <c r="B9" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="159" t="s">
+      <c r="C9" s="154" t="s">
         <v>261</v>
       </c>
-      <c r="D9" s="159" t="s">
+      <c r="D9" s="154" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="159"/>
-    </row>
-    <row r="12" spans="2:25" ht="14.4" thickBot="1">
-      <c r="B12" s="207" t="s">
+      <c r="E9" s="154"/>
+    </row>
+    <row r="12" spans="2:23" ht="14.25" thickBot="1">
+      <c r="B12" s="196" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="207"/>
-      <c r="D12" s="207"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="207"/>
-      <c r="G12" s="207"/>
-      <c r="H12" s="207"/>
-      <c r="I12" s="207"/>
-      <c r="J12" s="207"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="207"/>
-      <c r="Q12" s="207"/>
-      <c r="R12" s="207"/>
-      <c r="S12" s="207"/>
-      <c r="T12" s="207"/>
-      <c r="U12" s="207"/>
-      <c r="V12" s="207"/>
-    </row>
-    <row r="13" spans="2:25" ht="17.7">
-      <c r="B13" s="211" t="s">
+      <c r="C12" s="196"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="196"/>
+      <c r="F12" s="196"/>
+      <c r="G12" s="196"/>
+      <c r="H12" s="196"/>
+      <c r="I12" s="196"/>
+      <c r="J12" s="196"/>
+      <c r="K12" s="196"/>
+      <c r="L12" s="196"/>
+      <c r="M12" s="196"/>
+      <c r="N12" s="196"/>
+      <c r="O12" s="196"/>
+      <c r="P12" s="196"/>
+      <c r="Q12" s="196"/>
+      <c r="R12" s="196"/>
+      <c r="S12" s="196"/>
+      <c r="T12" s="196"/>
+      <c r="U12" s="196"/>
+      <c r="V12" s="196"/>
+    </row>
+    <row r="13" spans="2:23" ht="17.65">
+      <c r="B13" s="200" t="s">
         <v>205</v>
       </c>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="213"/>
-      <c r="I13" s="211" t="s">
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="201"/>
+      <c r="H13" s="202"/>
+      <c r="I13" s="200" t="s">
         <v>206</v>
       </c>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="212"/>
-      <c r="O13" s="213"/>
-      <c r="P13" s="211" t="s">
+      <c r="J13" s="201"/>
+      <c r="K13" s="201"/>
+      <c r="L13" s="201"/>
+      <c r="M13" s="201"/>
+      <c r="N13" s="201"/>
+      <c r="O13" s="202"/>
+      <c r="P13" s="200" t="s">
         <v>207</v>
       </c>
-      <c r="Q13" s="214"/>
-      <c r="R13" s="214"/>
-      <c r="S13" s="214"/>
-      <c r="T13" s="214"/>
-      <c r="U13" s="214"/>
-      <c r="V13" s="215"/>
-      <c r="W13" s="209" t="s">
+      <c r="Q13" s="203"/>
+      <c r="R13" s="203"/>
+      <c r="S13" s="203"/>
+      <c r="T13" s="203"/>
+      <c r="U13" s="203"/>
+      <c r="V13" s="204"/>
+      <c r="W13" s="198" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="2:25" ht="25.2">
-      <c r="B14" s="216" t="s">
+    <row r="14" spans="2:23" ht="25.5">
+      <c r="B14" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="217"/>
-      <c r="D14" s="116" t="s">
+      <c r="C14" s="206"/>
+      <c r="D14" s="114" t="s">
         <v>192</v>
       </c>
-      <c r="E14" s="116" t="s">
+      <c r="E14" s="114" t="s">
         <v>193</v>
       </c>
-      <c r="F14" s="116" t="s">
+      <c r="F14" s="114" t="s">
         <v>194</v>
       </c>
-      <c r="G14" s="116" t="s">
+      <c r="G14" s="114" t="s">
         <v>195</v>
       </c>
-      <c r="H14" s="117" t="s">
+      <c r="H14" s="115" t="s">
         <v>196</v>
       </c>
-      <c r="I14" s="216" t="s">
+      <c r="I14" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="J14" s="217"/>
-      <c r="K14" s="116" t="s">
+      <c r="J14" s="206"/>
+      <c r="K14" s="114" t="s">
         <v>192</v>
       </c>
-      <c r="L14" s="116" t="s">
+      <c r="L14" s="114" t="s">
         <v>197</v>
       </c>
-      <c r="M14" s="116" t="s">
+      <c r="M14" s="114" t="s">
         <v>194</v>
       </c>
-      <c r="N14" s="116" t="s">
+      <c r="N14" s="114" t="s">
         <v>195</v>
       </c>
-      <c r="O14" s="117" t="s">
+      <c r="O14" s="115" t="s">
         <v>196</v>
       </c>
-      <c r="P14" s="216" t="s">
+      <c r="P14" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="Q14" s="218"/>
-      <c r="R14" s="116" t="s">
+      <c r="Q14" s="207"/>
+      <c r="R14" s="114" t="s">
         <v>192</v>
       </c>
       <c r="S14" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="T14" s="116" t="s">
+      <c r="T14" s="114" t="s">
         <v>194</v>
       </c>
       <c r="U14" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="V14" s="117" t="s">
+      <c r="V14" s="115" t="s">
         <v>196</v>
       </c>
-      <c r="W14" s="210"/>
-    </row>
-    <row r="15" spans="2:25" ht="25.2">
-      <c r="B15" s="111" t="s">
+      <c r="W14" s="199"/>
+    </row>
+    <row r="15" spans="2:23" ht="25.5">
+      <c r="B15" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="C15" s="112" t="s">
+      <c r="C15" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="113" t="s">
+      <c r="E15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="113" t="s">
+      <c r="G15" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="H15" s="114" t="s">
+      <c r="H15" s="113" t="s">
         <v>201</v>
       </c>
-      <c r="I15" s="111" t="s">
+      <c r="I15" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="112" t="s">
+      <c r="J15" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="K15" s="113" t="s">
+      <c r="K15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="113" t="s">
+      <c r="L15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="M15" s="113" t="s">
+      <c r="M15" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="113" t="s">
+      <c r="N15" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="O15" s="114" t="s">
+      <c r="O15" s="113" t="s">
         <v>201</v>
       </c>
-      <c r="P15" s="111" t="s">
+      <c r="P15" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="Q15" s="112" t="s">
+      <c r="Q15" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="R15" s="113" t="s">
+      <c r="R15" s="112" t="s">
         <v>202</v>
       </c>
-      <c r="S15" s="113" t="s">
+      <c r="S15" s="112" t="s">
         <v>202</v>
       </c>
-      <c r="T15" s="113" t="s">
+      <c r="T15" s="112" t="s">
         <v>202</v>
       </c>
-      <c r="U15" s="113" t="s">
+      <c r="U15" s="112" t="s">
         <v>203</v>
       </c>
-      <c r="V15" s="114" t="s">
+      <c r="V15" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="W15" s="118" t="s">
+      <c r="W15" s="116" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="16" spans="2:25">
-      <c r="B16" s="120">
+    <row r="16" spans="2:23">
+      <c r="B16" s="1">
         <v>21</v>
       </c>
-      <c r="C16" s="120">
+      <c r="C16" s="1">
         <v>22</v>
       </c>
-      <c r="D16" s="120">
+      <c r="D16" s="1">
         <v>23</v>
       </c>
-      <c r="E16" s="120">
+      <c r="E16" s="1">
         <v>24</v>
       </c>
-      <c r="F16" s="120">
+      <c r="F16" s="1">
         <v>25</v>
       </c>
-      <c r="G16" s="120">
+      <c r="G16" s="1">
         <v>26</v>
       </c>
-      <c r="H16" s="120">
+      <c r="H16" s="1">
         <v>27</v>
       </c>
-      <c r="I16" s="120">
+      <c r="I16" s="1">
         <v>31</v>
       </c>
-      <c r="J16" s="120">
+      <c r="J16" s="1">
         <v>32</v>
       </c>
-      <c r="K16" s="120">
+      <c r="K16" s="1">
         <v>33</v>
       </c>
-      <c r="L16" s="120">
+      <c r="L16" s="1">
         <v>34</v>
       </c>
-      <c r="M16" s="120">
+      <c r="M16" s="1">
         <v>35</v>
       </c>
-      <c r="N16" s="120">
+      <c r="N16" s="1">
         <v>36</v>
       </c>
-      <c r="O16" s="120">
+      <c r="O16" s="1">
         <v>37</v>
       </c>
-      <c r="P16" s="153" t="e">
+      <c r="P16" s="148" t="e">
         <f>(B16*G16+I16*N16)/U16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" s="92"/>
-      <c r="R16" s="92"/>
-      <c r="S16" s="92"/>
-      <c r="T16" s="92"/>
-      <c r="U16" s="92"/>
-      <c r="V16" s="92"/>
-      <c r="W16" s="92"/>
-      <c r="Y16" s="92"/>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="154">
+      <c r="B19" s="149">
         <v>99</v>
       </c>
-      <c r="C19" s="155">
+      <c r="C19" s="150">
         <v>65</v>
       </c>
-      <c r="D19" s="155">
+      <c r="D19" s="150">
         <v>1.2</v>
       </c>
-      <c r="E19" s="155">
+      <c r="E19" s="150">
         <v>99</v>
       </c>
-      <c r="F19" s="155">
+      <c r="F19" s="150">
         <v>0.25</v>
       </c>
-      <c r="G19" s="155">
+      <c r="G19" s="150">
         <v>2254</v>
       </c>
-      <c r="H19" s="156">
+      <c r="H19" s="151">
         <f>B19*G19/100</f>
         <v>2231.46</v>
       </c>
-      <c r="I19" s="154">
+      <c r="I19" s="149">
         <v>92.3</v>
       </c>
-      <c r="J19" s="155">
+      <c r="J19" s="150">
         <v>88.9</v>
       </c>
-      <c r="K19" s="155">
+      <c r="K19" s="150">
         <v>3.6</v>
       </c>
-      <c r="L19" s="155">
+      <c r="L19" s="150">
         <v>99.5</v>
       </c>
-      <c r="M19" s="155">
+      <c r="M19" s="150">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N19" s="155">
+      <c r="N19" s="150">
         <v>150</v>
       </c>
-      <c r="O19" s="156">
+      <c r="O19" s="151">
         <f>I19*N19/100</f>
         <v>138.44999999999999</v>
       </c>
-      <c r="P19" s="153">
+      <c r="P19" s="148">
         <f>(B19*G19+I19*N19)/U19</f>
         <v>98.581946755407657</v>
       </c>
-      <c r="Q19" s="157">
+      <c r="Q19" s="152">
         <f>(C19*G19+J19*N19)/U19</f>
         <v>66.491264559068213</v>
       </c>
-      <c r="R19" s="157">
+      <c r="R19" s="152">
         <f>(D19*G19+K19*N19)/U19</f>
         <v>1.3497504159733775</v>
       </c>
-      <c r="S19" s="157">
+      <c r="S19" s="152">
         <f>(E19*G19+L19*N19)/U19</f>
         <v>99.031198003327788</v>
       </c>
-      <c r="T19" s="157">
+      <c r="T19" s="152">
         <f>(F19*G19+M19*N19)/U19</f>
         <v>0.49022462562396008</v>
       </c>
-      <c r="U19" s="157">
+      <c r="U19" s="152">
         <f>G19+N19</f>
         <v>2404</v>
       </c>
-      <c r="V19" s="158">
+      <c r="V19" s="153">
         <f>H19+O19</f>
         <v>2369.91</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="208"/>
+      <c r="D26" s="197"/>
+      <c r="E26" s="197"/>
+      <c r="F26" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -10073,50 +10231,50 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="B2:Q7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="15.6484375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.19921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="14" width="6.59765625" style="2" customWidth="1"/>
     <col min="15" max="16" width="7.59765625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="187"/>
-      <c r="N2" s="187"/>
-      <c r="O2" s="187"/>
-      <c r="P2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
+      <c r="N2" s="176"/>
+      <c r="O2" s="176"/>
+      <c r="P2" s="176"/>
     </row>
     <row r="3" spans="2:16" ht="15" customHeight="1">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
-      <c r="L3" s="186"/>
-      <c r="M3" s="186"/>
-      <c r="N3" s="186"/>
-      <c r="O3" s="186"/>
-      <c r="P3" s="186"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="175"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="175"/>
     </row>
     <row r="4" spans="2:16" ht="60" customHeight="1">
       <c r="B4" s="61" t="s">
@@ -10166,45 +10324,25 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="60" customHeight="1">
-      <c r="B5" s="160" t="s">
+      <c r="B5" s="155" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="38">
-        <v>26.80645179748535</v>
-      </c>
+      <c r="C5" s="38"/>
       <c r="D5" s="38">
         <v>26.806455612182617</v>
       </c>
       <c r="E5" s="38">
         <v>26.806455612182617</v>
       </c>
-      <c r="F5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="G5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="H5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="I5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="J5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="K5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="L5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="M5" s="38">
-        <v>26.806455612182617</v>
-      </c>
-      <c r="N5" s="38">
-        <v>26.806455612182617</v>
-      </c>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
       <c r="O5" s="38">
         <v>26.806453704833984</v>
       </c>
@@ -10213,45 +10351,25 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="60" customHeight="1">
-      <c r="B6" s="161" t="s">
+      <c r="B6" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="62"/>
+      <c r="D6" s="62">
         <v>620</v>
-      </c>
-      <c r="D6" s="62">
-        <v>616.125</v>
       </c>
       <c r="E6" s="62">
         <v>616.125</v>
       </c>
-      <c r="F6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="G6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="H6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="I6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="J6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="K6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="L6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="M6" s="62">
-        <v>616.125</v>
-      </c>
-      <c r="N6" s="62">
-        <v>616.125</v>
-      </c>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
       <c r="O6" s="62">
         <v>620</v>
       </c>
@@ -10259,7 +10377,7 @@
         <v>612.25</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="25" customHeight="1">
+    <row r="7" spans="2:16" ht="25.05" customHeight="1">
       <c r="B7" s="2" t="s">
         <v>279</v>
       </c>
@@ -10281,104 +10399,104 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="B2:N25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.84765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.59765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="15.94921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.9296875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="12" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
     </row>
     <row r="3" spans="2:13" ht="30" customHeight="1">
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="211" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-      <c r="K3" s="218"/>
-      <c r="L3" s="218"/>
-      <c r="M3" s="205"/>
-    </row>
-    <row r="4" spans="2:13" ht="10" customHeight="1">
-      <c r="B4" s="223"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="225"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
+      <c r="M3" s="194"/>
+    </row>
+    <row r="4" spans="2:13" ht="10.05" customHeight="1">
+      <c r="B4" s="212"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="214"/>
     </row>
     <row r="5" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B5" s="226" t="s">
+      <c r="B5" s="215" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="227" t="s">
+      <c r="C5" s="216" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="K5" s="228" t="s">
+      <c r="K5" s="217" t="s">
         <v>127</v>
       </c>
-      <c r="L5" s="228" t="s">
+      <c r="L5" s="217" t="s">
         <v>126</v>
       </c>
-      <c r="M5" s="229" t="s">
+      <c r="M5" s="218" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="215" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="227"/>
+      <c r="C6" s="216"/>
       <c r="D6" s="5" t="s">
         <v>122</v>
       </c>
@@ -10400,25 +10518,25 @@
       <c r="J6" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="227"/>
-      <c r="L6" s="227"/>
-      <c r="M6" s="206"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="195"/>
     </row>
     <row r="7" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B7" s="219" t="s">
+      <c r="B7" s="208" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="220"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="220"/>
-      <c r="F7" s="220"/>
-      <c r="G7" s="220"/>
-      <c r="H7" s="220"/>
-      <c r="I7" s="220"/>
-      <c r="J7" s="220"/>
-      <c r="K7" s="220"/>
-      <c r="L7" s="220"/>
-      <c r="M7" s="221"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="209"/>
+      <c r="I7" s="209"/>
+      <c r="J7" s="209"/>
+      <c r="K7" s="209"/>
+      <c r="L7" s="209"/>
+      <c r="M7" s="210"/>
     </row>
     <row r="8" spans="2:13" ht="20.1" customHeight="1">
       <c r="B8" s="4" t="s">
@@ -10427,7 +10545,7 @@
       <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="152">
+      <c r="D8" s="147">
         <v>11</v>
       </c>
       <c r="E8" s="5">
@@ -10456,7 +10574,7 @@
       </c>
       <c r="M8" s="6">
         <f>K8-L8</f>
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="20.1" customHeight="1">
@@ -10466,7 +10584,7 @@
       <c r="C9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="152">
+      <c r="D9" s="147">
         <v>13</v>
       </c>
       <c r="E9" s="5">
@@ -10505,7 +10623,7 @@
       <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="152">
+      <c r="D10" s="147">
         <v>17</v>
       </c>
       <c r="E10" s="5">
@@ -10538,20 +10656,20 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B11" s="219" t="s">
+      <c r="B11" s="208" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="220"/>
-      <c r="D11" s="220"/>
-      <c r="E11" s="220"/>
-      <c r="F11" s="220"/>
-      <c r="G11" s="220"/>
-      <c r="H11" s="220"/>
-      <c r="I11" s="220"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="220"/>
-      <c r="L11" s="220"/>
-      <c r="M11" s="221"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="209"/>
+      <c r="F11" s="209"/>
+      <c r="G11" s="209"/>
+      <c r="H11" s="209"/>
+      <c r="I11" s="209"/>
+      <c r="J11" s="209"/>
+      <c r="K11" s="209"/>
+      <c r="L11" s="209"/>
+      <c r="M11" s="210"/>
     </row>
     <row r="12" spans="2:13" ht="20.1" customHeight="1">
       <c r="B12" s="4" t="s">
@@ -10560,7 +10678,7 @@
       <c r="C12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="89">
+      <c r="D12" s="88">
         <v>26.80645179748535</v>
       </c>
       <c r="E12" s="5">
@@ -10599,7 +10717,7 @@
       <c r="C13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="89">
+      <c r="D13" s="88">
         <v>0</v>
       </c>
       <c r="E13" s="5">
@@ -10632,13 +10750,13 @@
       </c>
     </row>
     <row r="14" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B14" s="162" t="s">
+      <c r="B14" s="157" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="163">
+      <c r="D14" s="158">
         <v>29.80645179748535</v>
       </c>
       <c r="E14" s="5">
@@ -10719,121 +10837,121 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B16" s="219" t="s">
+      <c r="B16" s="208" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="209"/>
+      <c r="G16" s="209"/>
+      <c r="H16" s="209"/>
+      <c r="I16" s="209"/>
+      <c r="J16" s="209"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="210"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.1" customHeight="1">
+      <c r="B17" s="169" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="170" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="E17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="F17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="G17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="H17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="I17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="J17" s="170">
+        <v>166.19998168945312</v>
+      </c>
+      <c r="K17" s="170">
+        <v>620</v>
+      </c>
+      <c r="L17" s="170">
+        <v>612.25</v>
+      </c>
+      <c r="M17" s="171"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.1" customHeight="1">
+      <c r="B18" s="169" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="170" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="170">
+        <v>63</v>
+      </c>
+      <c r="E18" s="170">
+        <v>63</v>
+      </c>
+      <c r="F18" s="170">
+        <v>63</v>
+      </c>
+      <c r="G18" s="170">
+        <v>63</v>
+      </c>
+      <c r="H18" s="170">
+        <v>63</v>
+      </c>
+      <c r="I18" s="170">
+        <v>63</v>
+      </c>
+      <c r="J18" s="170">
+        <v>63</v>
+      </c>
+      <c r="K18" s="170">
+        <v>166.19996643066406</v>
+      </c>
+      <c r="L18" s="170">
+        <v>164.12246704101562</v>
+      </c>
+      <c r="M18" s="171">
+        <f>K18-L18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="20.1" customHeight="1">
+      <c r="B19" s="208" t="s">
         <v>287</v>
       </c>
-      <c r="C16" s="220"/>
-      <c r="D16" s="220"/>
-      <c r="E16" s="220"/>
-      <c r="F16" s="220"/>
-      <c r="G16" s="220"/>
-      <c r="H16" s="220"/>
-      <c r="I16" s="220"/>
-      <c r="J16" s="220"/>
-      <c r="K16" s="220"/>
-      <c r="L16" s="220"/>
-      <c r="M16" s="221"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B17" s="174" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="175" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="E17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="F17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="G17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="H17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="I17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="J17" s="175">
-        <v>166.19998168945312</v>
-      </c>
-      <c r="K17" s="175">
-        <v>620</v>
-      </c>
-      <c r="L17" s="175">
-        <v>612.25</v>
-      </c>
-      <c r="M17" s="176"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B18" s="174" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="175" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="175">
-        <v>63</v>
-      </c>
-      <c r="E18" s="175">
-        <v>63</v>
-      </c>
-      <c r="F18" s="175">
-        <v>63</v>
-      </c>
-      <c r="G18" s="175">
-        <v>63</v>
-      </c>
-      <c r="H18" s="175">
-        <v>63</v>
-      </c>
-      <c r="I18" s="175">
-        <v>63</v>
-      </c>
-      <c r="J18" s="175">
-        <v>63</v>
-      </c>
-      <c r="K18" s="175">
-        <v>166.19996643066406</v>
-      </c>
-      <c r="L18" s="175">
-        <v>164.12246704101562</v>
-      </c>
-      <c r="M18" s="176">
-        <f>K18-L18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B19" s="219" t="s">
-        <v>288</v>
-      </c>
-      <c r="C19" s="220"/>
-      <c r="D19" s="220"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="220"/>
-      <c r="G19" s="220"/>
-      <c r="H19" s="220"/>
-      <c r="I19" s="220"/>
-      <c r="J19" s="220"/>
-      <c r="K19" s="220"/>
-      <c r="L19" s="220"/>
-      <c r="M19" s="221"/>
+      <c r="C19" s="209"/>
+      <c r="D19" s="209"/>
+      <c r="E19" s="209"/>
+      <c r="F19" s="209"/>
+      <c r="G19" s="209"/>
+      <c r="H19" s="209"/>
+      <c r="I19" s="209"/>
+      <c r="J19" s="209"/>
+      <c r="K19" s="209"/>
+      <c r="L19" s="209"/>
+      <c r="M19" s="210"/>
     </row>
     <row r="20" spans="2:13" ht="20.1" customHeight="1">
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="159" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="120" t="s">
-        <v>283</v>
+      <c r="D20" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -10853,8 +10971,8 @@
       </c>
     </row>
     <row r="21" spans="2:13" ht="20.1" customHeight="1">
-      <c r="D21" s="120" t="s">
-        <v>283</v>
+      <c r="D21" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="20.1" customHeight="1"/>
@@ -10885,43 +11003,44 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="B2:J15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.34765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="7" width="13.34765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.59765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="30" customHeight="1">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" customHeight="1">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="233"/>
-    </row>
-    <row r="5" spans="2:9" ht="25" customHeight="1">
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="222"/>
+    </row>
+    <row r="5" spans="2:9" ht="25.05" customHeight="1">
       <c r="B5" s="4" t="s">
         <v>39</v>
       </c>
@@ -10941,7 +11060,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="25" customHeight="1">
+    <row r="6" spans="2:9" ht="25.05" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>40</v>
       </c>
@@ -10961,7 +11080,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="25" customHeight="1">
+    <row r="7" spans="2:9" ht="25.05" customHeight="1">
       <c r="B7" s="79" t="s">
         <v>81</v>
       </c>
@@ -10982,7 +11101,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="25" customHeight="1">
+    <row r="8" spans="2:9" ht="25.05" customHeight="1">
       <c r="B8" s="77" t="s">
         <v>209</v>
       </c>
@@ -10993,6 +11112,7 @@
         <v>116</v>
       </c>
       <c r="E8" s="78">
+        <f>C8/D8</f>
         <v>0</v>
       </c>
       <c r="F8" s="71">
@@ -11002,7 +11122,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="25" customHeight="1">
+    <row r="9" spans="2:9" ht="25.05" customHeight="1">
       <c r="B9" s="77" t="s">
         <v>90</v>
       </c>
@@ -11013,6 +11133,7 @@
         <v>116</v>
       </c>
       <c r="E9" s="78">
+        <f>C9/D9</f>
         <v>0</v>
       </c>
       <c r="F9" s="71">
@@ -11029,94 +11150,98 @@
       </c>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1">
-      <c r="B10" s="234" t="s">
+      <c r="B10" s="223" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="236"/>
-    </row>
-    <row r="11" spans="2:9" ht="25" customHeight="1">
+      <c r="C10" s="224"/>
+      <c r="D10" s="224"/>
+      <c r="E10" s="224"/>
+      <c r="F10" s="224"/>
+      <c r="G10" s="225"/>
+    </row>
+    <row r="11" spans="2:9" ht="25.05" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="311" t="s">
+      <c r="C11" s="226" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="216"/>
+      <c r="E11" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="179" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="2:9" ht="25" customHeight="1">
+    </row>
+    <row r="12" spans="2:9" ht="25.05" customHeight="1">
       <c r="B12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="311" t="s">
+      <c r="C12" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="216"/>
+      <c r="E12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="179" t="s">
+      <c r="F12" s="54"/>
+      <c r="G12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="96"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="2:9" ht="25" customHeight="1">
+    </row>
+    <row r="13" spans="2:9" ht="25.05" customHeight="1">
       <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="312">
+      <c r="C13" s="227">
         <v>41</v>
       </c>
-      <c r="D13" s="313">
+      <c r="D13" s="228">
         <v>43</v>
       </c>
-      <c r="E13" s="314">
+      <c r="E13" s="95">
         <v>45</v>
       </c>
-      <c r="F13" s="314"/>
-      <c r="G13" s="315"/>
-    </row>
-    <row r="14" spans="2:9" ht="25" customHeight="1">
+      <c r="F13" s="97"/>
+      <c r="G13" s="88"/>
+    </row>
+    <row r="14" spans="2:9" ht="25.05" customHeight="1">
       <c r="B14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="316">
+      <c r="C14" s="229">
         <v>41</v>
       </c>
-      <c r="D14" s="317">
+      <c r="D14" s="230">
         <v>43</v>
       </c>
-      <c r="E14" s="314">
+      <c r="E14" s="96">
         <v>45</v>
       </c>
-      <c r="F14" s="314"/>
-      <c r="G14" s="318"/>
-    </row>
-    <row r="15" spans="2:9" ht="25" customHeight="1">
-      <c r="C15" s="230" t="s">
+      <c r="F14" s="98"/>
+      <c r="G14" s="89"/>
+    </row>
+    <row r="15" spans="2:9" ht="25.05" customHeight="1">
+      <c r="C15" s="219" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="230"/>
-      <c r="E15" s="230"/>
-      <c r="F15" s="230"/>
-      <c r="G15" s="230"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="219"/>
+      <c r="F15" s="219"/>
+      <c r="G15" s="219"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="B3:G3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
